--- a/templates/20-financial-analysis-template.xlsx
+++ b/templates/20-financial-analysis-template.xlsx
@@ -2,8 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Blank template" sheetId="2" r:id="rId2"/>
+    <sheet name="Blank template" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -448,114 +447,6 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="92" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10.20  Financial Analysis</t>
-        </is>
-      </c>
-      <c r="B1" s="5"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Valuation and decision</t>
-        </is>
-      </c>
-      <c r="B2" s="8"/>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">What it is for</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Puts a monetary frame around a change: what it costs, what it returns, when the return arrives and what the money is worth once timing and risk are accounted for.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reach for it when</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reach for it whenever an option has to be justified in money, or when two options differ mainly in the timing of their costs and benefits rather than in their size.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confused with</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Financial analysis values what is already forecast; estimation produces the forecast. And a positive return is not the same as the best option: the exam repeatedly offers an option that is profitable but beaten by an alternative.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tasks</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.4 Define Change Strategy  ·  7.6 Analyze Potential Value and Recommend Solution  ·  8.5 Recommend Actions to Increase Solution Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Knowledge areas</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6, 7, 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The blank template is on the next sheet — fill it in.</t>
-        </is>
-      </c>
-      <c r="B10" s="6"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A10:B10"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
